--- a/excel_routes/route_YNB_CAI_threats.xlsx
+++ b/excel_routes/route_YNB_CAI_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -50,12 +50,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -77,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -86,9 +80,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -456,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -532,12 +523,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>06-JUN-26</t>
+          <t>25-JUL-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SM-448</t>
+          <t>SM-442</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -546,13 +537,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>430</v>
+        <v>340</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>432</v>
+        <v>418</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-2</v>
+        <v>-78</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -577,7 +568,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -591,13 +582,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>671</v>
+        <v>340</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>810</v>
+        <v>418</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-139</v>
+        <v>-78</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -622,12 +613,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>01-AUG-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SM-442</t>
+          <t>SM-448</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -636,13 +627,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>763</v>
+        <v>340</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>810</v>
+        <v>418</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-47</v>
+        <v>-78</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -667,12 +658,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>27-JUN-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SM-448</t>
+          <t>SM-442</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -681,13 +672,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>763</v>
+        <v>340</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>930</v>
+        <v>418</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-167</v>
+        <v>-78</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -712,7 +703,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>30-JUN-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -726,13 +717,13 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>763</v>
+        <v>340</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1170</v>
+        <v>418</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-407</v>
+        <v>-78</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -743,9 +734,9 @@
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -757,7 +748,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>04-JUL-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -771,13 +762,13 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1271</v>
+        <v>340</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1380</v>
+        <v>418</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-109</v>
+        <v>-78</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -802,7 +793,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>15-AUG-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -816,13 +807,13 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>971</v>
+        <v>340</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1170</v>
+        <v>418</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-199</v>
+        <v>-78</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -847,12 +838,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>11-JUL-26</t>
+          <t>15-AUG-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>SM-442</t>
+          <t>SM-448</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -861,13 +852,13 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1101</v>
+        <v>340</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1170</v>
+        <v>477</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-69</v>
+        <v>-137</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -884,456 +875,6 @@
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>14-JUL-26</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>SM-442</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-104</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>671</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>810</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>-139</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>21-JUL-26</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>SM-442</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-104</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>571</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>600</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>-29</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>25-JUL-26</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>SM-442</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-104</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>571</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>600</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>-29</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>01-AUG-26</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>SM-442</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-104</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>571</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>600</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>-29</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>04-AUG-26</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>SM-442</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-104</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>571</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>600</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>-29</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>08-AUG-26</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>SM-442</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-104</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>571</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>600</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>-29</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>11-AUG-26</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>SM-442</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-104</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>571</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>600</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>-29</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>15-AUG-26</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>SM-442</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-104</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>571</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>600</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>-29</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>22-SEP-26</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>SM-442</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-104</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>571</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>1050</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>-479</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>26-SEP-26</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>SM-442</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-104</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>571</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>1050</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>-479</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_YNB_CAI_threats.xlsx
+++ b/excel_routes/route_YNB_CAI_threats.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_260726_at_14.46\reports\excel_routes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_270726_at_12.25\reports\excel_routes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{100533C8-3353-450B-93A3-264128A5B131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{452E40A6-EE60-4A9F-AA7D-57412B5E81A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12972" yWindow="348" windowWidth="10068" windowHeight="10284" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="26">
   <si>
     <t>Date</t>
   </si>
@@ -79,6 +79,9 @@
   </si>
   <si>
     <t>SM-448</t>
+  </si>
+  <si>
+    <t>04-AUG-26</t>
   </si>
   <si>
     <t>08-AUG-26</t>
@@ -487,7 +490,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -714,10 +717,10 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>13</v>
@@ -726,10 +729,10 @@
         <v>340</v>
       </c>
       <c r="E7" s="2">
-        <v>477</v>
+        <v>418</v>
       </c>
       <c r="F7" s="2">
-        <v>-137</v>
+        <v>-78</v>
       </c>
       <c r="G7" s="2">
         <v>30</v>
@@ -752,7 +755,7 @@
         <v>21</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>13</v>
@@ -796,10 +799,10 @@
         <v>340</v>
       </c>
       <c r="E9" s="2">
-        <v>418</v>
+        <v>477</v>
       </c>
       <c r="F9" s="2">
-        <v>-78</v>
+        <v>-137</v>
       </c>
       <c r="G9" s="2">
         <v>30</v>
@@ -884,6 +887,41 @@
         <v>14</v>
       </c>
       <c r="K11" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="2">
+        <v>340</v>
+      </c>
+      <c r="E12" s="2">
+        <v>418</v>
+      </c>
+      <c r="F12" s="2">
+        <v>-78</v>
+      </c>
+      <c r="G12" s="2">
+        <v>30</v>
+      </c>
+      <c r="H12" s="2">
+        <v>30</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K12" s="2" t="s">
         <v>15</v>
       </c>
     </row>
